--- a/src/data/Backup/RISE_photos.xlsx
+++ b/src/data/Backup/RISE_photos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JamieJudd\repo\Resight\Resight Website\Series One Microsite\rise-series-one-microsite\src\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JamieJudd\repo\Resight\Resight Website\Series One Microsite\rise-series-one-microsite\src\data\Backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4475A0D0-47C5-46AB-BFAD-70D9E286DD6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B93E70-B9BB-48B7-B56D-20139110A40E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4095" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{7DF75F37-EE62-459D-B4D6-E535EA05D855}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9460" windowHeight="14730" xr2:uid="{7DF75F37-EE62-459D-B4D6-E535EA05D855}"/>
   </bookViews>
   <sheets>
     <sheet name="RISE_lawyers" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="468">
   <si>
     <t>Name</t>
   </si>
@@ -50,207 +50,132 @@
     <t>IND00602</t>
   </si>
   <si>
-    <t>Photos/Vijayendra-Pratap-Singh_5792526_1.jpg</t>
-  </si>
-  <si>
     <t>Vijayendra Pratap Singh</t>
   </si>
   <si>
     <t>IND00589</t>
   </si>
   <si>
-    <t>Photos/Rajendra-Barot_5789029_1.jpg</t>
-  </si>
-  <si>
     <t>Rajendra Barot</t>
   </si>
   <si>
     <t>IND00386</t>
   </si>
   <si>
-    <t>Photos/Shaneen-Parikh-updated.png</t>
-  </si>
-  <si>
     <t>Shaneen Parikh</t>
   </si>
   <si>
     <t>IND00761</t>
   </si>
   <si>
-    <t>Photos/Nitesh Jain.png</t>
-  </si>
-  <si>
     <t>Nitesh Jain</t>
   </si>
   <si>
-    <t>IND02504</t>
-  </si>
-  <si>
-    <t>Photos/Vyapak Desai - Arb.jpg</t>
-  </si>
-  <si>
     <t>Vyapak Desai</t>
   </si>
   <si>
     <t>IND00456</t>
   </si>
   <si>
-    <t>Photos/ila-kapur.png</t>
-  </si>
-  <si>
     <t>Ila Kapoor</t>
   </si>
   <si>
     <t>IND00439</t>
   </si>
   <si>
-    <t>Photos/Binsy Susan.png</t>
-  </si>
-  <si>
     <t>Binsy Susan</t>
   </si>
   <si>
     <t>IND00112</t>
   </si>
   <si>
-    <t>Photos/Kingshuk.png</t>
-  </si>
-  <si>
     <t>Kingshuk Banerjee</t>
   </si>
   <si>
     <t>IND00020</t>
   </si>
   <si>
-    <t>Photos/Ajay Bhargava_0.png</t>
-  </si>
-  <si>
     <t>Ajay Bhargava</t>
   </si>
   <si>
     <t>IND00788</t>
   </si>
   <si>
-    <t>Photos/shankh-sengupta-1.png</t>
-  </si>
-  <si>
     <t>Shankh Sengupta</t>
   </si>
   <si>
     <t>IND01508</t>
   </si>
   <si>
-    <t>Photos/Naresh Thacker.jpg</t>
-  </si>
-  <si>
     <t>Naresh Thacker</t>
   </si>
   <si>
     <t>IND00337</t>
   </si>
   <si>
-    <t>Photos/Kapil Arora - Arb.png</t>
-  </si>
-  <si>
     <t>Kapil Arora</t>
   </si>
   <si>
-    <t>IND07512</t>
-  </si>
-  <si>
-    <t>Photos/Manoj K Singh.png</t>
-  </si>
-  <si>
     <t>Manoj K Singh</t>
   </si>
   <si>
     <t>IND02631</t>
   </si>
   <si>
-    <t>Photos/Gunita_Pahwa.jpg</t>
-  </si>
-  <si>
     <t>Gunita Pahwa</t>
   </si>
   <si>
     <t>IND00712</t>
   </si>
   <si>
-    <t>Photos/ashish-bhan.png</t>
-  </si>
-  <si>
     <t>Ashish Bhan</t>
   </si>
   <si>
     <t>IND00801</t>
   </si>
   <si>
-    <t>Photos/tine-abraham-1.png</t>
-  </si>
-  <si>
     <t>Tine Abraham</t>
   </si>
   <si>
     <t>IND01936</t>
   </si>
   <si>
-    <t>Photos/Dheeraj-Nair-profile-picture-1200x432.jpg</t>
-  </si>
-  <si>
     <t>Dheeraj Nair</t>
   </si>
   <si>
     <t>IND02739</t>
   </si>
   <si>
-    <t>Photos/Manmeet Singh.png</t>
-  </si>
-  <si>
     <t>Manmeet Singh</t>
   </si>
   <si>
     <t>IND00327</t>
   </si>
   <si>
-    <t>Photos/Indranil.png</t>
-  </si>
-  <si>
     <t>Indranil Deshmukh</t>
   </si>
   <si>
     <t>IND02569</t>
   </si>
   <si>
-    <t>Photos/Suvigya Awasthy.png</t>
-  </si>
-  <si>
     <t>Suvigya Awasthy</t>
   </si>
   <si>
     <t>IND00929</t>
   </si>
   <si>
-    <t>Photos/SameerTapia.JPG</t>
-  </si>
-  <si>
     <t>Sameer Tapia</t>
   </si>
   <si>
     <t>IND00540</t>
   </si>
   <si>
-    <t>Photos/smarika-Singh.png</t>
-  </si>
-  <si>
     <t>Smarika Singh</t>
   </si>
   <si>
     <t>IND00663</t>
   </si>
   <si>
-    <t>Photos/Priyanka-Shetty-copy-1-e1633778843896.jpg</t>
-  </si>
-  <si>
     <t>Priyanka Shetty</t>
   </si>
   <si>
@@ -266,852 +191,552 @@
     <t>IND01048</t>
   </si>
   <si>
-    <t>Photos/Sneha Jaisingh.jpg</t>
-  </si>
-  <si>
     <t>Sneha Jaisingh</t>
   </si>
   <si>
     <t>IND00739</t>
   </si>
   <si>
-    <t>Photos/Ketan-Gaur.png</t>
-  </si>
-  <si>
     <t>Ketan Gaur</t>
   </si>
   <si>
-    <t>IND07515</t>
-  </si>
-  <si>
-    <t>Photos/Ashim Sood.jpg</t>
-  </si>
-  <si>
     <t>Ashim Sood</t>
   </si>
   <si>
-    <t>IND07574</t>
-  </si>
-  <si>
-    <t>Photos/Sooraj Sharma.png</t>
-  </si>
-  <si>
     <t>Sooraj Sharma</t>
   </si>
   <si>
     <t>IND00064</t>
   </si>
   <si>
-    <t>Photos/Chakrapani Mishra 2025 web.png</t>
-  </si>
-  <si>
     <t>Chakrapani Misra</t>
   </si>
   <si>
     <t>IND00502</t>
   </si>
   <si>
-    <t>Photos/prashant-Gupta.png</t>
-  </si>
-  <si>
     <t>Prashant Gupta</t>
   </si>
   <si>
     <t>IND01732</t>
   </si>
   <si>
-    <t>Photos/Manan-Lahoty.jpg</t>
-  </si>
-  <si>
     <t>Manan Lahoty</t>
   </si>
   <si>
     <t>IND03123</t>
   </si>
   <si>
-    <t>Photos/Yash-Ashar - ECM.png</t>
-  </si>
-  <si>
     <t>Yash J. Ashar</t>
   </si>
   <si>
     <t>IND02634</t>
   </si>
   <si>
-    <t>Photos/Sandip-Bhagat-GS-scaled.jpg</t>
-  </si>
-  <si>
     <t>Sandip Bhagat</t>
   </si>
   <si>
     <t>IND00777</t>
   </si>
   <si>
-    <t>Photos/Richa Choudhary.png</t>
-  </si>
-  <si>
     <t>Richa Choudhary</t>
   </si>
   <si>
     <t>IND00494</t>
   </si>
   <si>
-    <t>Photos/nikhil-naredi.png</t>
-  </si>
-  <si>
     <t>Nikhil Naredi</t>
   </si>
   <si>
     <t>IND00715</t>
   </si>
   <si>
-    <t>Photos/bhakta-patnaik-1.png</t>
-  </si>
-  <si>
     <t>Bhakta Patnaik</t>
   </si>
   <si>
     <t>IND00005</t>
   </si>
   <si>
-    <t>Photos/Abhimanyu-Bhattacharya.png</t>
-  </si>
-  <si>
     <t>Abhimanyu Bhattacharya</t>
   </si>
   <si>
     <t>IND03138</t>
   </si>
   <si>
-    <t>Photos/Vijay-Parthasarathi.png</t>
-  </si>
-  <si>
     <t>Vijay Parthasarathi</t>
   </si>
   <si>
     <t>IND00271</t>
   </si>
   <si>
-    <t>Photos/abhinav-2.png</t>
-  </si>
-  <si>
     <t>Abhinav Kumar</t>
   </si>
   <si>
     <t>IND01915</t>
   </si>
   <si>
-    <t>Photos/Arka-Mookerjee-Profile-Picture.jpg</t>
-  </si>
-  <si>
     <t>Arka Mookerjee</t>
   </si>
   <si>
     <t>IND02635</t>
   </si>
   <si>
-    <t>Photos/Jabarati-Chandra-GS.jpeg</t>
-  </si>
-  <si>
     <t>Jabarati Chandra</t>
   </si>
   <si>
     <t>IND01774</t>
   </si>
   <si>
-    <t>Photos/Vishal-Yaduvanshi.png</t>
-  </si>
-  <si>
     <t>Vishal Yaduvanshi</t>
   </si>
   <si>
     <t>IND00016</t>
   </si>
   <si>
-    <t>Photos/Aditya Cheriyan.png</t>
-  </si>
-  <si>
     <t>Aditya George Cheriyan</t>
   </si>
   <si>
     <t>IND01975</t>
   </si>
   <si>
-    <t>Photos/Madhurima-Mukherjee-profile-picture.jpg</t>
-  </si>
-  <si>
     <t>Madhurima Mukherjee (Saha)</t>
   </si>
   <si>
     <t>IND00601</t>
   </si>
   <si>
-    <t>Photos/Varoon Chandra - ECM.jpg</t>
-  </si>
-  <si>
     <t>Varoon Chandra</t>
   </si>
   <si>
     <t>IND00229</t>
   </si>
   <si>
-    <t>Photos/Sudghir Bassi.png</t>
-  </si>
-  <si>
     <t>Sudhir Bassi</t>
   </si>
   <si>
     <t>IND00579</t>
   </si>
   <si>
-    <t>Photos/Lionel-D_Almeida_5789015_1.jpg</t>
-  </si>
-  <si>
     <t>Lionel D'Almeida</t>
   </si>
   <si>
     <t>IND00090</t>
   </si>
   <si>
-    <t>Photos/Gautham Srinivas web 2025.png</t>
-  </si>
-  <si>
     <t>Gautham Srinivas</t>
   </si>
   <si>
     <t>IND00323</t>
   </si>
   <si>
-    <t>Photos/Gokul-Rajan-1.png</t>
-  </si>
-  <si>
     <t>Gokul Rajan</t>
   </si>
   <si>
     <t>IND02649</t>
   </si>
   <si>
-    <t>Photos/Jitesh-Shahani-GS.jpeg</t>
-  </si>
-  <si>
     <t>Jitesh Shahani</t>
   </si>
   <si>
     <t>IND01752</t>
   </si>
   <si>
-    <t>Photos/Ravi-Dubey.png</t>
-  </si>
-  <si>
     <t>Ravi Dubey</t>
   </si>
   <si>
     <t>IND00698</t>
   </si>
   <si>
-    <t>Photos/Albin-Thomas-1.png</t>
-  </si>
-  <si>
     <t>Albin Thomas</t>
   </si>
   <si>
     <t>IND06252</t>
   </si>
   <si>
-    <t>Photos/Aashima-Johur.png</t>
-  </si>
-  <si>
     <t>Aashima Johur</t>
   </si>
   <si>
     <t>IND02650</t>
   </si>
   <si>
-    <t>Photos/Juhi-Singh-GS-1.jpg</t>
-  </si>
-  <si>
     <t>Juhi Singh</t>
   </si>
   <si>
     <t>IND00371</t>
   </si>
   <si>
-    <t>Photos/Reuben Chacko - ECM.jpg</t>
-  </si>
-  <si>
     <t>Reuben Chacko</t>
   </si>
   <si>
     <t>IND03708</t>
   </si>
   <si>
-    <t>Photos/Abhinav Maver - ECM.png</t>
-  </si>
-  <si>
     <t>Abhinav Maker</t>
   </si>
   <si>
     <t>IND01046</t>
   </si>
   <si>
-    <t>Photos/Vishnu Dutt.jpg</t>
-  </si>
-  <si>
     <t>Vishnu Dutt U</t>
   </si>
   <si>
     <t>IND02647</t>
   </si>
   <si>
-    <t>Photos/Pratichi-Mishra-GS.jpeg</t>
-  </si>
-  <si>
     <t>Pratichi Mishra</t>
   </si>
   <si>
     <t>IND01705</t>
   </si>
   <si>
-    <t>Photos/Abhiroop-Lahiri-.png</t>
-  </si>
-  <si>
     <t>Abhiroop Lahiri</t>
   </si>
   <si>
     <t>IND00245</t>
   </si>
   <si>
-    <t>Photos/Thomas George.png</t>
-  </si>
-  <si>
     <t>Thomas George</t>
   </si>
   <si>
     <t>IND02009</t>
   </si>
   <si>
-    <t>Photos/Pracheta-Bhattacharya-profile-picture.jpg</t>
-  </si>
-  <si>
     <t>Pracheta Bhattacharya</t>
   </si>
   <si>
     <t>IND00552</t>
   </si>
   <si>
-    <t>Photos/Veena-Final.png</t>
-  </si>
-  <si>
     <t>Veena Sivaramakrishnan</t>
   </si>
   <si>
     <t>IND01744</t>
   </si>
   <si>
-    <t>Photos/Priyadarshini-Rao.png</t>
-  </si>
-  <si>
     <t>Priyadarshini Rao</t>
   </si>
   <si>
     <t>IND00140</t>
   </si>
   <si>
-    <t>Photos/Oishik Bagchi_0.png</t>
-  </si>
-  <si>
     <t>Oishik Bagchi</t>
   </si>
   <si>
     <t>IND00716</t>
   </si>
   <si>
-    <t>Photos/Brajendu-bhaskar.png</t>
-  </si>
-  <si>
     <t>Brajendu Bhaskar</t>
   </si>
   <si>
     <t>IND00406</t>
   </si>
   <si>
-    <t>Photos/Abhiroop-Amitava-Datta- ECM.png</t>
-  </si>
-  <si>
     <t>Abhiroop Datta</t>
   </si>
   <si>
     <t>IND03141</t>
   </si>
   <si>
-    <t>Photos/vinay-sirohia.png</t>
-  </si>
-  <si>
     <t>Vinay Sirohia</t>
   </si>
   <si>
-    <t>IND07590</t>
-  </si>
-  <si>
-    <t>Photos/Prashaant Rajput.jpg</t>
-  </si>
-  <si>
     <t>IND00004</t>
   </si>
   <si>
-    <t>Photos/Ayush Mohata - ECM.png</t>
-  </si>
-  <si>
     <t>Aayush Mohata</t>
   </si>
   <si>
     <t>IND00120</t>
   </si>
   <si>
-    <t>Photos/Manisha Shroff.png</t>
-  </si>
-  <si>
     <t>Manisha Shroff</t>
   </si>
   <si>
     <t>IND02109</t>
   </si>
   <si>
-    <t>Photos/Uttara-M.-Kolhatkar-profile-picture-1024x369.jpg</t>
-  </si>
-  <si>
     <t>Uttara M. Kolhatkar</t>
   </si>
   <si>
     <t>IND00536</t>
   </si>
   <si>
-    <t>Photos/shubhangi-garg.png</t>
-  </si>
-  <si>
     <t>Shubhangi Garg</t>
   </si>
   <si>
     <t>IND04763</t>
   </si>
   <si>
-    <t>Photos/Pranav Sharma - CAM.jpg</t>
-  </si>
-  <si>
     <t>Pranav Sharma</t>
   </si>
   <si>
     <t>IND02940</t>
   </si>
   <si>
-    <t>Photos/Priyanka-Kumar-2.jpg</t>
-  </si>
-  <si>
     <t>Priyanka Kumar</t>
   </si>
   <si>
     <t>IND02962</t>
   </si>
   <si>
-    <t>Photos/Rahul-Gulati- DCM.jpg</t>
-  </si>
-  <si>
     <t>Rahul Gulati</t>
   </si>
   <si>
-    <t>IND07528</t>
-  </si>
-  <si>
-    <t>Photos/Niloufer Lam.webp</t>
-  </si>
-  <si>
     <t>Niloufer Lam</t>
   </si>
   <si>
     <t>IND02534</t>
   </si>
   <si>
-    <t>Photos/Aditya Bhargava.png</t>
-  </si>
-  <si>
     <t>Aditya Bhargava</t>
   </si>
   <si>
     <t>IND00398</t>
   </si>
   <si>
-    <t>Photos/Subhalakshmi Naskar.jpg</t>
-  </si>
-  <si>
     <t>Subhalakshmi Naskar</t>
   </si>
   <si>
     <t>IND02750</t>
   </si>
   <si>
-    <t>Photos/Satadru-Goswami.png</t>
-  </si>
-  <si>
     <t>Satadru Goswami</t>
   </si>
   <si>
     <t>IND00759</t>
   </si>
   <si>
-    <t>Photos/Nisha-Kaur-Uberoi-profile-picture.jpg</t>
-  </si>
-  <si>
     <t>Nisha Kaur Uberoi</t>
   </si>
   <si>
     <t>IND00454</t>
   </si>
   <si>
-    <t>Photos/harman-singh-sandhu.png</t>
-  </si>
-  <si>
     <t>Harman Singh Sandhu</t>
   </si>
   <si>
     <t>IND00301</t>
   </si>
   <si>
-    <t>Photos/avantika kakkar.jpg</t>
-  </si>
-  <si>
     <t>Avaantika Kakkar</t>
   </si>
   <si>
     <t>IND01030</t>
   </si>
   <si>
-    <t>Photos/Samir Gandhi.png</t>
-  </si>
-  <si>
     <t>Samir R Gandhi</t>
   </si>
   <si>
     <t>IND01160</t>
   </si>
   <si>
-    <t>Photos/Karan Chandhiok.jpg</t>
-  </si>
-  <si>
     <t>Karan Chandhiok</t>
   </si>
   <si>
     <t>IND00590</t>
   </si>
   <si>
-    <t>Photos/Ram-Kumar-Poornachandran.png</t>
-  </si>
-  <si>
     <t>Ram Kumar Poornachandran</t>
   </si>
   <si>
     <t>IND00553</t>
   </si>
   <si>
-    <t>Photos/yaman-verma.png</t>
-  </si>
-  <si>
     <t>Yaman Verma</t>
   </si>
   <si>
     <t>IND00038</t>
   </si>
   <si>
-    <t>Photos/Anshuman Sakle 2025 web_0.png</t>
-  </si>
-  <si>
     <t>Anshuman Sakle</t>
   </si>
   <si>
     <t>IND01031</t>
   </si>
   <si>
-    <t>Photos/rahul rai.png</t>
-  </si>
-  <si>
     <t>Rahul Rai</t>
   </si>
   <si>
     <t>IND00628</t>
   </si>
   <si>
-    <t>Photos/Bharat-Budholia-e1637655967207.png</t>
-  </si>
-  <si>
     <t>Bharat Budholia</t>
   </si>
   <si>
     <t>IND00490</t>
   </si>
   <si>
-    <t>Photos/naval-chopra.png</t>
-  </si>
-  <si>
     <t>Naval Satarawala Chopra</t>
   </si>
   <si>
     <t>IND00537</t>
   </si>
   <si>
-    <t>Photos/Shweta-Shroff.png</t>
-  </si>
-  <si>
     <t>Shweta Shroff Chopra</t>
   </si>
   <si>
     <t>IND00118</t>
   </si>
   <si>
-    <t>Photos/Manas Kumar Chaudhuri.png</t>
-  </si>
-  <si>
     <t>Manas Kumar Chaudhuri</t>
   </si>
   <si>
     <t>IND00639</t>
   </si>
   <si>
-    <t>Photos/Hemangini-dadwal-3.jpg</t>
-  </si>
-  <si>
     <t>Hemangini Dadwal</t>
   </si>
   <si>
     <t>IND00033</t>
   </si>
   <si>
-    <t>Photos/Anisha Chand.jpg</t>
-  </si>
-  <si>
     <t>Anisha Chand</t>
   </si>
   <si>
     <t>IND01516</t>
   </si>
   <si>
-    <t>Photos/Ravisekhar Nair.jpg</t>
-  </si>
-  <si>
     <t>Ravisekhar Nair</t>
   </si>
   <si>
     <t>IND00780</t>
   </si>
   <si>
-    <t>Photos/Rudresh-Singh.png</t>
-  </si>
-  <si>
     <t>Rudresh Singh</t>
   </si>
   <si>
     <t>IND00428</t>
   </si>
   <si>
-    <t>Photos/Aparna Mehra.png</t>
-  </si>
-  <si>
     <t>Aparna Mehra</t>
   </si>
   <si>
     <t>IND02110</t>
   </si>
   <si>
-    <t>Vabhav-Choukse_profile-picture.jpg</t>
-  </si>
-  <si>
     <t>Vaibhav Choukse</t>
   </si>
   <si>
     <t>IND01161</t>
   </si>
   <si>
-    <t>Photos/Deeksha manchanda.jpg</t>
-  </si>
-  <si>
     <t>Deeksha Manchanda</t>
   </si>
   <si>
     <t>IND00726</t>
   </si>
   <si>
-    <t>Photos/gautam-chawla-1.png</t>
-  </si>
-  <si>
     <t>Gautam Chawla</t>
   </si>
   <si>
     <t>IND02948</t>
   </si>
   <si>
-    <t>Photos/Sonam Mathur.jpg</t>
-  </si>
-  <si>
     <t>Sonam Mathur</t>
   </si>
   <si>
     <t>IND00153</t>
   </si>
   <si>
-    <t>Photos/Pranjal Prateek_0.png</t>
-  </si>
-  <si>
     <t>Pranjal Prateek</t>
   </si>
   <si>
     <t>IND04713</t>
   </si>
   <si>
-    <t>Photos/Kirthi-Srinivas-Website-1.jpg</t>
-  </si>
-  <si>
     <t>Kirthi Srinivas</t>
   </si>
   <si>
     <t>IND00314</t>
   </si>
   <si>
-    <t>Photos/Dhruv-Rajain.png</t>
-  </si>
-  <si>
     <t>Dhruv Rajain</t>
   </si>
   <si>
     <t>IND00511</t>
   </si>
   <si>
-    <t>Photos/Rohan-Arora.png</t>
-  </si>
-  <si>
     <t>Rohan Arora</t>
   </si>
   <si>
     <t>IND00451</t>
   </si>
   <si>
-    <t>Photos/Gauri-Chhabra.png</t>
-  </si>
-  <si>
     <t>Gauri Chhabra</t>
   </si>
   <si>
-    <t>IND07656</t>
-  </si>
-  <si>
-    <t>Photos/abir-roy-neww.png</t>
-  </si>
-  <si>
     <t>Abir Roy</t>
   </si>
   <si>
     <t>IND00966</t>
   </si>
   <si>
-    <t>Photos/Rahul Goel.jpg</t>
-  </si>
-  <si>
     <t>Rahul Goel</t>
   </si>
   <si>
     <t>IND01511</t>
   </si>
   <si>
-    <t>Photos/Parthsarathi Jha.jpg</t>
-  </si>
-  <si>
     <t>Parthsarathi Jha</t>
   </si>
   <si>
     <t>IND01150</t>
   </si>
   <si>
-    <t>Photos/Avinash Amarnath.jpg</t>
-  </si>
-  <si>
     <t>Avinash Amarnath</t>
   </si>
   <si>
     <t>IND00968</t>
   </si>
   <si>
-    <t>Photos/Anu Monga.jpg</t>
-  </si>
-  <si>
     <t>Anu Monga</t>
   </si>
   <si>
     <t>IND01943</t>
   </si>
   <si>
-    <t>Photos/Ela-Bali-profile-picture-1200x432.jpg</t>
-  </si>
-  <si>
     <t>Ela Bali</t>
   </si>
   <si>
     <t>IND03139</t>
   </si>
   <si>
-    <t>Photos/Vijay-Pratap-Singh-Chauhan.png</t>
-  </si>
-  <si>
     <t>Vijay Pratap Singh Chauhan</t>
   </si>
   <si>
     <t>IND02231</t>
   </si>
   <si>
-    <t>Photos/Neelambera Sandeepan.jpg</t>
-  </si>
-  <si>
     <t>Neelambera Sandeepan</t>
   </si>
   <si>
     <t>IND02909</t>
   </si>
   <si>
-    <t>Photos/Gaurav-Desai.png</t>
-  </si>
-  <si>
     <t>Gaurav Desai</t>
   </si>
   <si>
     <t>IND02652</t>
   </si>
   <si>
-    <t>Photos/Simran-Dhir-GS.jpg</t>
-  </si>
-  <si>
     <t>Simran Dhir</t>
   </si>
   <si>
     <t>IND01474</t>
   </si>
   <si>
-    <t>Photos/Mr-Abhay-Joshi.jpg</t>
-  </si>
-  <si>
     <t>Abhay Joshi</t>
   </si>
   <si>
     <t>IND01772</t>
   </si>
   <si>
-    <t>Photos/Unnati-Agrawal-Copy.png</t>
-  </si>
-  <si>
     <t>Unnati Agrawal</t>
   </si>
   <si>
     <t>IND02656</t>
   </si>
   <si>
-    <t>Photos/Akshat-Kulshrestha-GS.jpg</t>
-  </si>
-  <si>
     <t>Akshat Kulshrestha</t>
   </si>
   <si>
@@ -1127,9 +752,6 @@
     <t>IND03226</t>
   </si>
   <si>
-    <t>Mathew Chacko.jpg</t>
-  </si>
-  <si>
     <t>Mathew Chacko</t>
   </si>
   <si>
@@ -1160,48 +782,27 @@
     <t>Arun Prabhu</t>
   </si>
   <si>
-    <t>IND07527</t>
-  </si>
-  <si>
-    <t>Photos/Nehaa-Chaudhari.webp</t>
-  </si>
-  <si>
     <t>Nehaa Chaudhari</t>
   </si>
   <si>
     <t>IND02023</t>
   </si>
   <si>
-    <t>Probir ROy Chowdhaury.jpg</t>
-  </si>
-  <si>
     <t>Probir Roy Chowdhury</t>
   </si>
   <si>
-    <t>IND07530</t>
-  </si>
-  <si>
-    <t>Sreenidhi Srinivasan.jpg</t>
-  </si>
-  <si>
     <t>Sreenidhi Srinivasan</t>
   </si>
   <si>
     <t>IND02052</t>
   </si>
   <si>
-    <t>Sajai-Singh-Profile-Picture.jpg</t>
-  </si>
-  <si>
     <t>Sajai Singh</t>
   </si>
   <si>
     <t>IND01749</t>
   </si>
   <si>
-    <t>Ranjana Adhikari.jpg</t>
-  </si>
-  <si>
     <t>Ranjana Adhikari</t>
   </si>
   <si>
@@ -1217,9 +818,6 @@
     <t>IND04874</t>
   </si>
   <si>
-    <t>Akash Karmakar.jpg</t>
-  </si>
-  <si>
     <t>Akash Karmakar</t>
   </si>
   <si>
@@ -1235,9 +833,6 @@
     <t>IND01762</t>
   </si>
   <si>
-    <t>Shreya Suri.jpg</t>
-  </si>
-  <si>
     <t>Shreya Suri</t>
   </si>
   <si>
@@ -1253,912 +848,108 @@
     <t>IND05097</t>
   </si>
   <si>
-    <t>Aadya-Misra.webp</t>
-  </si>
-  <si>
     <t>Aadya Misra</t>
   </si>
   <si>
     <t>IND00291</t>
   </si>
   <si>
-    <t>Anirban Mohapatra.jpg</t>
-  </si>
-  <si>
     <t>Anirban Mohapatra</t>
   </si>
   <si>
     <t>IND01738</t>
   </si>
   <si>
-    <t>Namita Viswanathan.webp</t>
-  </si>
-  <si>
     <t>Namita Viswanath</t>
   </si>
   <si>
     <t>IND04894</t>
   </si>
   <si>
-    <t>Rishi-Anand.jpg</t>
-  </si>
-  <si>
     <t>Rishi Anand</t>
   </si>
   <si>
-    <t>IND07526</t>
-  </si>
-  <si>
-    <t>Utham Chengappa.jpg</t>
-  </si>
-  <si>
     <t>Utham Chengappa</t>
   </si>
   <si>
-    <t>IND00755</t>
-  </si>
-  <si>
-    <t>Photos/Neeraj-menon-1.png</t>
-  </si>
-  <si>
-    <t>Neeraj Menon</t>
-  </si>
-  <si>
-    <t>IND01897</t>
-  </si>
-  <si>
-    <t>Photos/Amit-Kapur-profile-picture-1024x369.jpg</t>
-  </si>
-  <si>
-    <t>Amit Kapur</t>
-  </si>
-  <si>
-    <t>IND00462</t>
-  </si>
-  <si>
-    <t>Photos/Jatin Aneja.png</t>
-  </si>
-  <si>
-    <t>Jatin Aneja</t>
-  </si>
-  <si>
-    <t>IND01697</t>
-  </si>
-  <si>
-    <t>Photos/Hemant Sahai.jpg</t>
-  </si>
-  <si>
-    <t>Hemant Sahai</t>
-  </si>
-  <si>
-    <t>IND00754</t>
-  </si>
-  <si>
-    <t>Photos/nayantara-nag.png</t>
-  </si>
-  <si>
-    <t>Nayantara Nag</t>
-  </si>
-  <si>
-    <t>IND00342</t>
-  </si>
-  <si>
-    <t>Photos/L Viswanathan.webp</t>
-  </si>
-  <si>
-    <t>L Viswanathan</t>
-  </si>
-  <si>
-    <t>IND00022</t>
-  </si>
-  <si>
-    <t>Photos/Akhil Bhatnagar_0.png</t>
-  </si>
-  <si>
-    <t>Akhil Bhatnagar</t>
-  </si>
-  <si>
-    <t>IND02732</t>
-  </si>
-  <si>
-    <t>Photos/Avirup-Nag-1.jpg</t>
-  </si>
-  <si>
-    <t>Avirup Nag</t>
-  </si>
-  <si>
-    <t>IND00568</t>
-  </si>
-  <si>
-    <t>Photos/Anuj Tiwari.webp</t>
-  </si>
-  <si>
-    <t>Anuja Tiwari</t>
-  </si>
-  <si>
-    <t>IND00079</t>
-  </si>
-  <si>
-    <t>Photos/Gahan Singh.png</t>
-  </si>
-  <si>
-    <t>Gahan Singh</t>
-  </si>
-  <si>
-    <t>IND02740</t>
-  </si>
-  <si>
-    <t>Photos/Mohit Saraf.png</t>
-  </si>
-  <si>
-    <t>Mohit Saraf</t>
-  </si>
-  <si>
-    <t>IND01264</t>
-  </si>
-  <si>
-    <t>Photos/Anjan-Dasgupta.jpg</t>
-  </si>
-  <si>
-    <t>Anjan Dasgupta</t>
-  </si>
-  <si>
-    <t>IND06176</t>
-  </si>
-  <si>
-    <t>Photos/Manasvini Raj.webp</t>
-  </si>
-  <si>
-    <t>Manasvini Raj</t>
-  </si>
-  <si>
-    <t>IND00070</t>
-  </si>
-  <si>
-    <t>Photos/Dibyanshu.png</t>
-  </si>
-  <si>
-    <t>Dibyanshu Sinha</t>
-  </si>
-  <si>
-    <t>IND00381</t>
-  </si>
-  <si>
-    <t>Photos/Sangita John.webp</t>
-  </si>
-  <si>
-    <t>Sangita John</t>
-  </si>
-  <si>
-    <t>IND00401</t>
-  </si>
-  <si>
-    <t>Photos/Surya Sreenivasan.webp</t>
-  </si>
-  <si>
-    <t>Surya Sreenivasan</t>
-  </si>
-  <si>
-    <t>IND00364</t>
-  </si>
-  <si>
-    <t>Ramanuj-Kumar-1.png</t>
-  </si>
-  <si>
-    <t>Ramanuj Kumar</t>
-  </si>
-  <si>
-    <t>IND02943</t>
-  </si>
-  <si>
-    <t>Photos/akshay-tta.jpg</t>
-  </si>
-  <si>
-    <t>Akshay Malhotra</t>
-  </si>
-  <si>
-    <t>IND01472</t>
-  </si>
-  <si>
-    <t>Photos/Aakanksha-Joshi-GS-3.jpg</t>
-  </si>
-  <si>
-    <t>Aakanksha Joshi</t>
-  </si>
-  <si>
-    <t>IND01701</t>
-  </si>
-  <si>
-    <t>Soumya-Kanti-De-Mallik-Partner.png</t>
-  </si>
-  <si>
-    <t>Soumya Malik</t>
-  </si>
-  <si>
-    <t>IND07529</t>
-  </si>
-  <si>
-    <t>Photos/Deepak-Sabharwal-683x1024.jpg</t>
-  </si>
-  <si>
-    <t>Deepak Sabharwal</t>
-  </si>
-  <si>
-    <t>IND00609</t>
-  </si>
-  <si>
-    <t>Photos/Aditya-Periwal.jpg</t>
-  </si>
-  <si>
-    <t>Aditya Periwal</t>
-  </si>
-  <si>
-    <t>IND02538</t>
-  </si>
-  <si>
-    <t>Photos/1688470766_pallavi-bedi.jpg</t>
-  </si>
-  <si>
-    <t>Pallavi Bedi</t>
-  </si>
-  <si>
-    <t>IND00211</t>
-  </si>
-  <si>
-    <t>Photos/Shivanshu Thaplyal.png</t>
-  </si>
-  <si>
-    <t>Shivanshu Thaplyal</t>
-  </si>
-  <si>
-    <t>IND00652</t>
-  </si>
-  <si>
-    <t>Photos/Mallika-Anand.png</t>
-  </si>
-  <si>
-    <t>Mallika Anand</t>
-  </si>
-  <si>
-    <t>IND00988</t>
-  </si>
-  <si>
-    <t>rajneet.jpg</t>
-  </si>
-  <si>
-    <t>Ranjit Prakash</t>
-  </si>
-  <si>
-    <t>IND00699</t>
-  </si>
-  <si>
-    <t>Photos/amar-narula-1.png</t>
-  </si>
-  <si>
-    <t>Amar Narula</t>
-  </si>
-  <si>
-    <t>IND06293</t>
-  </si>
-  <si>
-    <t>Photos/Gayatri-Shankar.png</t>
-  </si>
-  <si>
-    <t>Gayatri Shanker</t>
-  </si>
-  <si>
-    <t>IND00779</t>
-  </si>
-  <si>
-    <t>Photos/Riyaz-Bhagat.png</t>
-  </si>
-  <si>
-    <t>Riyaz Bhagat</t>
-  </si>
-  <si>
-    <t>IND02710</t>
-  </si>
-  <si>
-    <t>Photos/Sitara_Pillai-removebg-preview.avif</t>
-  </si>
-  <si>
-    <t>Sitara Pillai</t>
-  </si>
-  <si>
-    <t>IND02553</t>
-  </si>
-  <si>
-    <t>Photos/Sameer Jain.png</t>
-  </si>
-  <si>
-    <t>Sameer Jain</t>
-  </si>
-  <si>
-    <t>IND01692</t>
-  </si>
-  <si>
-    <t>Photos/Monali-Dutta.jpg</t>
-  </si>
-  <si>
-    <t>Monali Dutta</t>
-  </si>
-  <si>
-    <t>IND01504</t>
-  </si>
-  <si>
-    <t>Photos/Megha Agarwal-web.png</t>
-  </si>
-  <si>
-    <t>Megha Agarwal</t>
-  </si>
-  <si>
     <t>IND01522</t>
   </si>
   <si>
-    <t>Photos/Sanjay-Notani.jpg</t>
-  </si>
-  <si>
     <t>Sanjay Notani</t>
   </si>
   <si>
     <t>IND02274</t>
   </si>
   <si>
-    <t>Photos/v-lakshmikumaran-managing-partner-lakshmikumaran-sridharan-attorneys.jpg</t>
-  </si>
-  <si>
     <t>V. Lakshmikumaran</t>
   </si>
   <si>
     <t>IND02203</t>
   </si>
   <si>
-    <t>Photos/Devinder Bagia.jpg</t>
-  </si>
-  <si>
     <t>Devinder Bagia</t>
   </si>
   <si>
     <t>IND00723</t>
   </si>
   <si>
-    <t>Photos/dhruv-gupta-.png</t>
-  </si>
-  <si>
     <t>Dhruv Gupta</t>
   </si>
   <si>
-    <t>IND07689</t>
-  </si>
-  <si>
-    <t>Photos/Atul Sharma.png</t>
-  </si>
-  <si>
     <t>Atul Sharma</t>
   </si>
   <si>
-    <t>IND07621</t>
-  </si>
-  <si>
-    <t>Photos/Reena Khair.jpg</t>
-  </si>
-  <si>
     <t>Reena Khair</t>
   </si>
   <si>
-    <t>IND07657</t>
-  </si>
-  <si>
-    <t>Photos/Seetharaman Sampath.png</t>
-  </si>
-  <si>
     <t>Seetharaman Sampath</t>
   </si>
   <si>
-    <t>IND07570</t>
-  </si>
-  <si>
-    <t>Photos/Anuradha R V.jpg</t>
-  </si>
-  <si>
     <t>Anuradha R V</t>
   </si>
   <si>
     <t>IND02193</t>
   </si>
   <si>
-    <t>Photos/Ankur Sharma.jpg</t>
-  </si>
-  <si>
     <t>Ankur Sharma</t>
   </si>
   <si>
     <t>IND01267</t>
   </si>
   <si>
-    <t>Photos/Ashish-Chandra.jpg</t>
-  </si>
-  <si>
     <t>Ashish Chandra</t>
   </si>
   <si>
     <t>IND00121</t>
   </si>
   <si>
-    <t>Photos/Mayank Jain.png</t>
-  </si>
-  <si>
     <t>Mayank Jain</t>
   </si>
   <si>
     <t>IND00059</t>
   </si>
   <si>
-    <t>Photos/Ayush A Mehrotra.png</t>
-  </si>
-  <si>
     <t>Ayush Mehrotra</t>
   </si>
   <si>
     <t>IND02646</t>
   </si>
   <si>
-    <t>Photos/Ajinkya Gunjan Mishra.jpg</t>
-  </si>
-  <si>
     <t>Ajinkya Gunjan Mishra</t>
   </si>
   <si>
     <t>IND02989</t>
   </si>
   <si>
-    <t>Photos/Rajat Agarwal.jpg</t>
-  </si>
-  <si>
     <t>Rajat Agarwal</t>
   </si>
   <si>
     <t>IND00250</t>
   </si>
   <si>
-    <t>Photos/Udayan-Choksi.png</t>
-  </si>
-  <si>
     <t>Udayan Choksi</t>
   </si>
   <si>
-    <t>IND00569</t>
-  </si>
-  <si>
-    <t>Photos/Ashwath Rau.jpg</t>
-  </si>
-  <si>
-    <t>Ashwath Rau</t>
-  </si>
-  <si>
-    <t>IND00508</t>
-  </si>
-  <si>
-    <t>Photos/Raghubir Menon.png</t>
-  </si>
-  <si>
-    <t>Raghubir Menon</t>
-  </si>
-  <si>
-    <t>IND00370</t>
-  </si>
-  <si>
-    <t>Photos/Reeba Chacko.png</t>
-  </si>
-  <si>
-    <t>Reeba Chacko</t>
-  </si>
-  <si>
-    <t>IND00729</t>
-  </si>
-  <si>
-    <t>Photos/Harsh Maggon.png</t>
-  </si>
-  <si>
-    <t>Harsh Maggon</t>
-  </si>
-  <si>
-    <t>IND02118</t>
-  </si>
-  <si>
-    <t>Photos/Vikram Raghani.jpg</t>
-  </si>
-  <si>
-    <t>Vikram Raghani</t>
-  </si>
-  <si>
-    <t>IND00600</t>
-  </si>
-  <si>
-    <t>Photos/Vaidhyanandan Iyer.png</t>
-  </si>
-  <si>
-    <t>Vaidhyanadhan Iyer</t>
-  </si>
-  <si>
-    <t>IND00580</t>
-  </si>
-  <si>
-    <t>Photos/Nandish Vyas.png</t>
-  </si>
-  <si>
-    <t>Nandish Vyas</t>
-  </si>
-  <si>
-    <t>IND00092</t>
-  </si>
-  <si>
-    <t>Photos/Haigreve Khaitan.png</t>
-  </si>
-  <si>
-    <t>Haigreve Khaitan</t>
-  </si>
-  <si>
-    <t>IND00760</t>
-  </si>
-  <si>
-    <t>Photos/Nishant Parikh.png</t>
-  </si>
-  <si>
-    <t>Nishant Parikh</t>
-  </si>
-  <si>
-    <t>IND00391</t>
-  </si>
-  <si>
-    <t>Photos/Shishir Vattyaden.jpg</t>
-  </si>
-  <si>
-    <t>Shishir Jose Vayttaden</t>
-  </si>
-  <si>
-    <t>IND02937</t>
-  </si>
-  <si>
-    <t>Photos/Sonali Mahapatra.jpg</t>
-  </si>
-  <si>
-    <t>Sonali Mahapatra</t>
-  </si>
-  <si>
-    <t>IND00573</t>
-  </si>
-  <si>
-    <t>Photos/Darshika Kothari.jpg</t>
-  </si>
-  <si>
-    <t>Darshika Kothari</t>
-  </si>
-  <si>
-    <t>IND00782</t>
-  </si>
-  <si>
-    <t>Photos/Sai Krishna Barathan.png</t>
-  </si>
-  <si>
-    <t>Sai Krishna Bharathan</t>
-  </si>
-  <si>
-    <t>IND00566</t>
-  </si>
-  <si>
-    <t>Photos/Anil Kasturi.png</t>
-  </si>
-  <si>
-    <t>Anil Kasturi</t>
-  </si>
-  <si>
-    <t>IND02976</t>
-  </si>
-  <si>
-    <t>Photos/Abhijit Joshi.png</t>
-  </si>
-  <si>
-    <t>Abhijit Joshi</t>
-  </si>
-  <si>
-    <t>IND02949</t>
-  </si>
-  <si>
-    <t>Photos/Gautam Sahah.png</t>
-  </si>
-  <si>
-    <t>Gautam Saha</t>
-  </si>
-  <si>
-    <t>IND00736</t>
-  </si>
-  <si>
-    <t>Photos/Kannan Rahul.png</t>
-  </si>
-  <si>
-    <t>Kannan Rahul</t>
-  </si>
-  <si>
-    <t>IND00458</t>
-  </si>
-  <si>
-    <t>Photos/Iqbal Khan.png</t>
-  </si>
-  <si>
-    <t>Iqbal Khan</t>
-  </si>
-  <si>
-    <t>IND00369</t>
-  </si>
-  <si>
-    <t>Photos/Ravindra Bandhakavi.jpg</t>
-  </si>
-  <si>
-    <t>Ravindra Bandhakavi</t>
-  </si>
-  <si>
-    <t>IND00060</t>
-  </si>
-  <si>
-    <t>Photos/Bharat Anand.png</t>
-  </si>
-  <si>
-    <t>Bharat Anand</t>
-  </si>
-  <si>
-    <t>IND00132</t>
-  </si>
-  <si>
-    <t>Photos/Nikhil Narayanan.jpg</t>
-  </si>
-  <si>
-    <t>Nikhil Narayanan</t>
-  </si>
-  <si>
-    <t>IND00106</t>
-  </si>
-  <si>
-    <t>Photos/Kartick Maheshwari.png</t>
-  </si>
-  <si>
-    <t>Kartick Maheshwari</t>
-  </si>
-  <si>
-    <t>IND00463</t>
-  </si>
-  <si>
-    <t>Photos/Jay Gandhi.png</t>
-  </si>
-  <si>
-    <t>Jay Gandhi</t>
-  </si>
-  <si>
-    <t>IND00594</t>
-  </si>
-  <si>
-    <t>Photos/Roxanne Anderson.png</t>
-  </si>
-  <si>
-    <t>Roxanne Anderson</t>
-  </si>
-  <si>
-    <t>IND00356</t>
-  </si>
-  <si>
-    <t>Photos/Nivedita Rao.png</t>
-  </si>
-  <si>
-    <t>Nivedita Rao</t>
-  </si>
-  <si>
-    <t>IND00596</t>
-  </si>
-  <si>
-    <t>Photos/Srinath Dasari.jpg</t>
-  </si>
-  <si>
-    <t>Srinath Dasari</t>
-  </si>
-  <si>
-    <t>IND00164</t>
-  </si>
-  <si>
-    <t>Photos/Rabindra Jhunjhunwala.png</t>
-  </si>
-  <si>
-    <t>Rabindra Jhunjhunwala</t>
-  </si>
-  <si>
-    <t>IND00724</t>
-  </si>
-  <si>
-    <t>Photos/Ganesh Rao.png</t>
-  </si>
-  <si>
-    <t>Ganesh Rao</t>
-  </si>
-  <si>
-    <t>IND00218</t>
-  </si>
-  <si>
-    <t>Photos/Siddharth Shah.png</t>
-  </si>
-  <si>
-    <t>Siddarth Shah</t>
-  </si>
-  <si>
-    <t>IND00701</t>
-  </si>
-  <si>
-    <t>Photos/Amit Khansaheb.png</t>
-  </si>
-  <si>
-    <t>Amit Khansaheb</t>
-  </si>
-  <si>
-    <t>IND00477</t>
-  </si>
-  <si>
-    <t>Photos/Manish Gupta.png</t>
-  </si>
-  <si>
-    <t>Manish Gupta</t>
-  </si>
-  <si>
-    <t>IND00130</t>
-  </si>
-  <si>
-    <t>Photos/Nidhi Killawala.png</t>
-  </si>
-  <si>
-    <t>Nidhi Killawala</t>
-  </si>
-  <si>
-    <t>IND00074</t>
-  </si>
-  <si>
-    <t>Photos/Divaspati Singh.png</t>
-  </si>
-  <si>
-    <t>Divaspathi Singh</t>
-  </si>
-  <si>
-    <t>IND02476</t>
-  </si>
-  <si>
-    <t>Photos/Nishchal Joshipura.png</t>
-  </si>
-  <si>
-    <t>Nishchal Joshipura</t>
-  </si>
-  <si>
-    <t>IND00813</t>
-  </si>
-  <si>
-    <t>Photos/Yogesh Singh.png</t>
-  </si>
-  <si>
-    <t>Yogesh Singh</t>
-  </si>
-  <si>
-    <t>IND01232</t>
-  </si>
-  <si>
-    <t>Photos/Gunjan Shah.png</t>
-  </si>
-  <si>
-    <t>Gunjan Shah</t>
-  </si>
-  <si>
-    <t>IND00765</t>
-  </si>
-  <si>
-    <t>Photos/Pranav Atit.png</t>
-  </si>
-  <si>
-    <t>Pranav Atit</t>
-  </si>
-  <si>
-    <t>IND01707</t>
-  </si>
-  <si>
-    <t>Photos/Winnie Shekhar.jpg</t>
-  </si>
-  <si>
-    <t>Winnie Sherkhar</t>
-  </si>
-  <si>
-    <t>IND00582</t>
-  </si>
-  <si>
-    <t>Photos/Nanditha Gopal.jpg</t>
-  </si>
-  <si>
-    <t>Nanditha Gopal</t>
-  </si>
-  <si>
-    <t>IND03027</t>
-  </si>
-  <si>
-    <t>Photos/Siddhart Srivastava.png</t>
-  </si>
-  <si>
-    <t>Siddhart Srivastava</t>
-  </si>
-  <si>
-    <t>IND01737</t>
-  </si>
-  <si>
-    <t>Photos/Minhaz Lokhandwala.jpg</t>
-  </si>
-  <si>
-    <t>Minhaz Lokhandwala</t>
-  </si>
-  <si>
-    <t>IND00261</t>
-  </si>
-  <si>
-    <t>Photos/Vivek Mimani.png</t>
-  </si>
-  <si>
-    <t>Vivek Mamani</t>
-  </si>
-  <si>
-    <t>IND00696</t>
-  </si>
-  <si>
-    <t>Photos/Aditya Jha.png</t>
-  </si>
-  <si>
-    <t>Aditya Jha</t>
-  </si>
-  <si>
-    <t>IND01585</t>
-  </si>
-  <si>
-    <t>Photos/Shuva Mandal.jpg</t>
-  </si>
-  <si>
-    <t>Shuva Mandal</t>
-  </si>
-  <si>
-    <t>IND02506</t>
-  </si>
-  <si>
-    <t>Photos/Sharda Balaji.jpg</t>
-  </si>
-  <si>
-    <t>Sharda Balaji</t>
-  </si>
-  <si>
-    <t>IND00066</t>
-  </si>
-  <si>
-    <t>Photos/Deepak Jodhani.png</t>
-  </si>
-  <si>
-    <t>Deepak Jodhani</t>
-  </si>
-  <si>
-    <t>IND02081</t>
-  </si>
-  <si>
-    <t>Photos/Siddharth Mody.jpg</t>
-  </si>
-  <si>
-    <t>Siddharth Mody</t>
-  </si>
-  <si>
-    <t>IND00378</t>
-  </si>
-  <si>
-    <t>Photos/images.jpeg</t>
-  </si>
-  <si>
-    <t>S. Harish</t>
-  </si>
-  <si>
     <t>Prashaant Vikram Rajput</t>
   </si>
   <si>
@@ -2166,6 +957,486 @@
   </si>
   <si>
     <t>ResightID</t>
+  </si>
+  <si>
+    <t>Vijayendra-Pratap-Singh_5792526_1.png</t>
+  </si>
+  <si>
+    <t>Rajendra-Barot_5789029_1.png</t>
+  </si>
+  <si>
+    <t>Shaneen-Parikh-updated.png</t>
+  </si>
+  <si>
+    <t>Nitesh Jain.png</t>
+  </si>
+  <si>
+    <t>IND08607</t>
+  </si>
+  <si>
+    <t>Vyapak Desai - Arb.png</t>
+  </si>
+  <si>
+    <t>ila-kapur.png</t>
+  </si>
+  <si>
+    <t>Binsy Susan.png</t>
+  </si>
+  <si>
+    <t>Kingshuk.png</t>
+  </si>
+  <si>
+    <t>Ajay Bhargava_0.png</t>
+  </si>
+  <si>
+    <t>shankh-sengupta-1.png</t>
+  </si>
+  <si>
+    <t>Naresh Thacker.png</t>
+  </si>
+  <si>
+    <t>Kapil Arora - Arb.png</t>
+  </si>
+  <si>
+    <t>IND08608</t>
+  </si>
+  <si>
+    <t>Manoj K Singh.png</t>
+  </si>
+  <si>
+    <t>Gunita_Pahwa.png</t>
+  </si>
+  <si>
+    <t>ashish-bhan.png</t>
+  </si>
+  <si>
+    <t>tine-abraham-1.png</t>
+  </si>
+  <si>
+    <t>Dheeraj-Nair-profile-picture-1200x432.png</t>
+  </si>
+  <si>
+    <t>Manmeet Singh.png</t>
+  </si>
+  <si>
+    <t>Indranil.png</t>
+  </si>
+  <si>
+    <t>Suvigya Awasthy.png</t>
+  </si>
+  <si>
+    <t>SameerTapia.png</t>
+  </si>
+  <si>
+    <t>smarika-Singh.png</t>
+  </si>
+  <si>
+    <t>Priyanka-Shetty-copy-1-e1633778843896.png</t>
+  </si>
+  <si>
+    <t>Sneha Jaisingh.png</t>
+  </si>
+  <si>
+    <t>Ketan-Gaur.png</t>
+  </si>
+  <si>
+    <t>IND08609</t>
+  </si>
+  <si>
+    <t>Ashim Sood.png</t>
+  </si>
+  <si>
+    <t>IND08610</t>
+  </si>
+  <si>
+    <t>Sooraj Sharma.png</t>
+  </si>
+  <si>
+    <t>Chakrapani Mishra 2025 web.png</t>
+  </si>
+  <si>
+    <t>Manisha Shroff.png</t>
+  </si>
+  <si>
+    <t>Uttara-M.-Kolhatkar-profile-picture-1024x369.png</t>
+  </si>
+  <si>
+    <t>shubhangi-garg.png</t>
+  </si>
+  <si>
+    <t>Priyanka-Kumar-2.png</t>
+  </si>
+  <si>
+    <t>Pranav Sharma - CAM.png</t>
+  </si>
+  <si>
+    <t>Rahul-Gulati- DCM.png</t>
+  </si>
+  <si>
+    <t>Subhalakshmi Naskar.png</t>
+  </si>
+  <si>
+    <t>IND08612</t>
+  </si>
+  <si>
+    <t>Niloufer Lam.png</t>
+  </si>
+  <si>
+    <t>Veena-Final.png</t>
+  </si>
+  <si>
+    <t>Aditya Bhargava.png</t>
+  </si>
+  <si>
+    <t>Satadru-Goswami.png</t>
+  </si>
+  <si>
+    <t>prashant-Gupta.png</t>
+  </si>
+  <si>
+    <t>Manan-Lahoty.png</t>
+  </si>
+  <si>
+    <t>Yash-Ashar - ECM.png</t>
+  </si>
+  <si>
+    <t>Sandip-Bhagat-GS-scaled.png</t>
+  </si>
+  <si>
+    <t>Richa Choudhary.png</t>
+  </si>
+  <si>
+    <t>nikhil-naredi.png</t>
+  </si>
+  <si>
+    <t>bhakta-patnaik-1.png</t>
+  </si>
+  <si>
+    <t>Abhimanyu-Bhattacharya.png</t>
+  </si>
+  <si>
+    <t>Vijay-Parthasarathi.png</t>
+  </si>
+  <si>
+    <t>Abhinav-Kumar.png</t>
+  </si>
+  <si>
+    <t>Arka-Mookerjee-Profile-Picture.png</t>
+  </si>
+  <si>
+    <t>Jabarati-Chandra-GS.png</t>
+  </si>
+  <si>
+    <t>Vishal-Yaduvanshi.png</t>
+  </si>
+  <si>
+    <t>Aditya Cheriyan.png</t>
+  </si>
+  <si>
+    <t>Madhurima-Mukherjee-profile-picture.png</t>
+  </si>
+  <si>
+    <t>Varoon Chandra - ECM.png</t>
+  </si>
+  <si>
+    <t>Sudghir Bassi.png</t>
+  </si>
+  <si>
+    <t>Lionel-D_Almeida_5789015_1.png</t>
+  </si>
+  <si>
+    <t>Gautham Srinivas web 2025.png</t>
+  </si>
+  <si>
+    <t>Gokul-Rajan-1.png</t>
+  </si>
+  <si>
+    <t>Jitesh-Shahani-GS.png</t>
+  </si>
+  <si>
+    <t>Ravi-Dubey.png</t>
+  </si>
+  <si>
+    <t>Albin-Thomas-1.png</t>
+  </si>
+  <si>
+    <t>Aashima-Johur.png</t>
+  </si>
+  <si>
+    <t>Juhi-Singh-GS-1.png</t>
+  </si>
+  <si>
+    <t>Reuben Chacko - ECM.png</t>
+  </si>
+  <si>
+    <t>Abhinav Maver - ECM.png</t>
+  </si>
+  <si>
+    <t>Vishnu Dutt.png</t>
+  </si>
+  <si>
+    <t>Pratichi-Mishra-GS.png</t>
+  </si>
+  <si>
+    <t>Abhiroop-Lahiri-.png</t>
+  </si>
+  <si>
+    <t>Thomas George.png</t>
+  </si>
+  <si>
+    <t>Pracheta-Bhattacharya-profile-picture.png</t>
+  </si>
+  <si>
+    <t>Priyadarshini-Rao.png</t>
+  </si>
+  <si>
+    <t>Oishik Bagchi_0.png</t>
+  </si>
+  <si>
+    <t>Brajendu-bhaskar.png</t>
+  </si>
+  <si>
+    <t>Abhiroop-Amitava-Datta- ECM.png</t>
+  </si>
+  <si>
+    <t>vinay-sirohia.png</t>
+  </si>
+  <si>
+    <t>IND08611</t>
+  </si>
+  <si>
+    <t>Prashaant Rajput.png</t>
+  </si>
+  <si>
+    <t>Ayush Mohata - ECM.png</t>
+  </si>
+  <si>
+    <t>Nisha-Kaur-Uberoi-profile-picture.png</t>
+  </si>
+  <si>
+    <t>harman-singh-sandhu.png</t>
+  </si>
+  <si>
+    <t>avantika kakkar.png</t>
+  </si>
+  <si>
+    <t>Samir Gandhi.png</t>
+  </si>
+  <si>
+    <t>Karan Chandhiok.png</t>
+  </si>
+  <si>
+    <t>Ram-Kumar-Poornachandran.png</t>
+  </si>
+  <si>
+    <t>yaman-verma.png</t>
+  </si>
+  <si>
+    <t>Anshuman Sakle 2025 web_0.png</t>
+  </si>
+  <si>
+    <t>rahul rai.png</t>
+  </si>
+  <si>
+    <t>Bharat-Budholia-e1637655967207.png</t>
+  </si>
+  <si>
+    <t>naval-chopra.png</t>
+  </si>
+  <si>
+    <t>Shweta-Shroff.png</t>
+  </si>
+  <si>
+    <t>Manas Kumar Chaudhuri.png</t>
+  </si>
+  <si>
+    <t>Hemangini-dadwal-3.png</t>
+  </si>
+  <si>
+    <t>Anisha Chand.png</t>
+  </si>
+  <si>
+    <t>Ravisekhar Nair.png</t>
+  </si>
+  <si>
+    <t>Rudresh-Singh.png</t>
+  </si>
+  <si>
+    <t>Aparna Mehra.png</t>
+  </si>
+  <si>
+    <t>Vabhav-Choukse_profile-picture.png</t>
+  </si>
+  <si>
+    <t>Deeksha manchanda.png</t>
+  </si>
+  <si>
+    <t>gautam-chawla-1.png</t>
+  </si>
+  <si>
+    <t>Sonam Mathur.png</t>
+  </si>
+  <si>
+    <t>Pranjal Prateek_0.png</t>
+  </si>
+  <si>
+    <t>Kirthi-Srinivas-Website-1.png</t>
+  </si>
+  <si>
+    <t>Dhruv-Rajain.png</t>
+  </si>
+  <si>
+    <t>Rohan-Arora.png</t>
+  </si>
+  <si>
+    <t>Gauri-Chhabra.png</t>
+  </si>
+  <si>
+    <t>IND08613</t>
+  </si>
+  <si>
+    <t>abir-roy-neww.png</t>
+  </si>
+  <si>
+    <t>Rahul Goel.png</t>
+  </si>
+  <si>
+    <t>Parthsarathi Jha.png</t>
+  </si>
+  <si>
+    <t>Avinash Amarnath.png</t>
+  </si>
+  <si>
+    <t>Anu Monga.png</t>
+  </si>
+  <si>
+    <t>Ela-Bali-profile-picture-1200x432.png</t>
+  </si>
+  <si>
+    <t>Vijay-Pratap-Singh-Chauhan.png</t>
+  </si>
+  <si>
+    <t>Neelambera Sandeepan.png</t>
+  </si>
+  <si>
+    <t>Gaurav-Desai.png</t>
+  </si>
+  <si>
+    <t>Simran-Dhir-GS.png</t>
+  </si>
+  <si>
+    <t>Mr-Abhay-Joshi.png</t>
+  </si>
+  <si>
+    <t>Unnati-Agrawal-Copy.png</t>
+  </si>
+  <si>
+    <t>Akshat-Kulshrestha-GS.png</t>
+  </si>
+  <si>
+    <t>Mathew Chacko.png</t>
+  </si>
+  <si>
+    <t>IND08614</t>
+  </si>
+  <si>
+    <t>Nehaa-Chaudhari.png</t>
+  </si>
+  <si>
+    <t>Probir ROy Chowdhaury.png</t>
+  </si>
+  <si>
+    <t>IND08615</t>
+  </si>
+  <si>
+    <t>Sreenidhi Srinivasan.png</t>
+  </si>
+  <si>
+    <t>Sajai-Singh-Profile-Picture.png</t>
+  </si>
+  <si>
+    <t>Ranjana Adhikari.png</t>
+  </si>
+  <si>
+    <t>Akash Karmakar.png</t>
+  </si>
+  <si>
+    <t>Shreya Suri.png</t>
+  </si>
+  <si>
+    <t>Aadya-Misra.png</t>
+  </si>
+  <si>
+    <t>Anirban Mohapatra.png</t>
+  </si>
+  <si>
+    <t>Namita Viswanathan.png</t>
+  </si>
+  <si>
+    <t>Rishi-Anand.png</t>
+  </si>
+  <si>
+    <t>IND08616</t>
+  </si>
+  <si>
+    <t>Utham Chengappa.png</t>
+  </si>
+  <si>
+    <t>Sanjay-Notani.png</t>
+  </si>
+  <si>
+    <t>v-lakshmikumaran-managing-partner-lakshmikumaran-sridharan-attorneys.png</t>
+  </si>
+  <si>
+    <t>Devinder Bagia.png</t>
+  </si>
+  <si>
+    <t>dhruv-gupta-.png</t>
+  </si>
+  <si>
+    <t>IND08618</t>
+  </si>
+  <si>
+    <t>Atul Sharma.png</t>
+  </si>
+  <si>
+    <t>IND08619</t>
+  </si>
+  <si>
+    <t>Reena Khair.png</t>
+  </si>
+  <si>
+    <t>IND08620</t>
+  </si>
+  <si>
+    <t>Seetharaman Sampath.png</t>
+  </si>
+  <si>
+    <t>IND08621</t>
+  </si>
+  <si>
+    <t>Anuradha R V.png</t>
+  </si>
+  <si>
+    <t>Ankur Sharma.png</t>
+  </si>
+  <si>
+    <t>Ashish-Chandra.png</t>
+  </si>
+  <si>
+    <t>Mayank Jain.png</t>
+  </si>
+  <si>
+    <t>Ayush A Mehrotra.png</t>
+  </si>
+  <si>
+    <t>Ajinkya Gunjan Mishra.png</t>
+  </si>
+  <si>
+    <t>Rajat Agarwal.png</t>
+  </si>
+  <si>
+    <t>Udayan-Choksi.png</t>
   </si>
 </sst>
 </file>
@@ -3026,7 +2297,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F66F9B3D-2506-4708-A6BA-E03788ADC788}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="30.81640625" customWidth="1"/>
@@ -3035,10 +2306,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>710</v>
+        <v>307</v>
       </c>
       <c r="B1" t="s">
-        <v>709</v>
+        <v>306</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3046,849 +2317,849 @@
     </row>
     <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>135</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>391</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>359</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>365</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>317</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>406</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>297</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>464</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" t="s">
         <v>58</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>370</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>79</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>316</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>404</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>340</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>295</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>463</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>385</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>414</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>368</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>240</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>242</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>2</v>
+        <v>382</v>
       </c>
       <c r="C21" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>303</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>467</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>304</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>361</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s">
-        <v>68</v>
+        <v>444</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>394</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
-        <v>62</v>
+        <v>416</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>371</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>320</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>231</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>232</v>
+        <v>377</v>
       </c>
       <c r="C32" t="s">
-        <v>233</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>310</v>
       </c>
       <c r="C33" t="s">
-        <v>212</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>228</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>229</v>
+        <v>346</v>
       </c>
       <c r="C34" t="s">
-        <v>230</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>222</v>
+        <v>131</v>
       </c>
       <c r="B35" t="s">
-        <v>223</v>
+        <v>387</v>
       </c>
       <c r="C35" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>190</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>409</v>
       </c>
       <c r="C36" t="s">
-        <v>227</v>
+        <v>191</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>237</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>238</v>
+        <v>315</v>
       </c>
       <c r="C37" t="s">
-        <v>239</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>418</v>
       </c>
       <c r="C38" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>158</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>393</v>
       </c>
       <c r="C39" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
       <c r="B40" t="s">
-        <v>235</v>
+        <v>268</v>
       </c>
       <c r="C40" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>220</v>
+        <v>314</v>
       </c>
       <c r="C41" t="s">
-        <v>221</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>402</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>357</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>352</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="B46" t="s">
-        <v>170</v>
+        <v>342</v>
       </c>
       <c r="C46" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B47" t="s">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="C47" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>178</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>331</v>
       </c>
       <c r="C48" t="s">
-        <v>180</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>349</v>
       </c>
       <c r="C49" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
-        <v>158</v>
+        <v>398</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B51" t="s">
-        <v>122</v>
+        <v>369</v>
       </c>
       <c r="C51" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>309</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="B53" t="s">
-        <v>197</v>
+        <v>397</v>
       </c>
       <c r="C53" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>146</v>
+        <v>367</v>
       </c>
       <c r="C54" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>149</v>
+        <v>308</v>
       </c>
       <c r="C55" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="B56" t="s">
-        <v>125</v>
+        <v>401</v>
       </c>
       <c r="C56" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
-        <v>152</v>
+        <v>405</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>163</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>332</v>
       </c>
       <c r="C58" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>143</v>
+        <v>374</v>
       </c>
       <c r="C59" t="s">
-        <v>144</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>324</v>
       </c>
       <c r="C60" t="s">
-        <v>135</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="C61" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>386</v>
       </c>
       <c r="C62" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>193</v>
+        <v>285</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>452</v>
       </c>
       <c r="C63" t="s">
-        <v>195</v>
+        <v>286</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="B64" t="s">
-        <v>185</v>
+        <v>412</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s">
-        <v>206</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>708</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>91</v>
+        <v>243</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>93</v>
+        <v>245</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
+        <v>334</v>
       </c>
       <c r="C67" t="s">
-        <v>192</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="B68" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="C68" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>167</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>311</v>
       </c>
       <c r="C70" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>101</v>
+        <v>356</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="B72" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="C72" t="s">
-        <v>141</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>181</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>318</v>
       </c>
       <c r="C73" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>325</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>187</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>188</v>
+        <v>330</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="B76" t="s">
-        <v>116</v>
+        <v>421</v>
       </c>
       <c r="C76" t="s">
-        <v>117</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B77" t="s">
-        <v>203</v>
+        <v>424</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>127</v>
+        <v>162</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>395</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -3896,1751 +3167,863 @@
         <v>172</v>
       </c>
       <c r="B79" t="s">
+        <v>400</v>
+      </c>
+      <c r="C79" t="s">
         <v>173</v>
-      </c>
-      <c r="C79" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>379</v>
       </c>
       <c r="C80" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>176</v>
+        <v>333</v>
       </c>
       <c r="C81" t="s">
-        <v>177</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>351</v>
+        <v>215</v>
       </c>
       <c r="B82" t="s">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="C82" t="s">
-        <v>353</v>
+        <v>216</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>321</v>
+        <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="C83" t="s">
-        <v>323</v>
+        <v>165</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>357</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="C84" t="s">
-        <v>359</v>
+        <v>195</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B85" t="s">
-        <v>283</v>
+        <v>462</v>
       </c>
       <c r="C85" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="B86" t="s">
-        <v>262</v>
+        <v>430</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>291</v>
+        <v>23</v>
       </c>
       <c r="B87" t="s">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="C87" t="s">
-        <v>293</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="B88" t="s">
-        <v>247</v>
+        <v>422</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>330</v>
+        <v>186</v>
       </c>
       <c r="B89" t="s">
-        <v>331</v>
+        <v>407</v>
       </c>
       <c r="C89" t="s">
-        <v>332</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="B90" t="s">
-        <v>268</v>
+        <v>449</v>
       </c>
       <c r="C90" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>297</v>
+        <v>117</v>
       </c>
       <c r="B91" t="s">
-        <v>298</v>
+        <v>381</v>
       </c>
       <c r="C91" t="s">
-        <v>299</v>
+        <v>118</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>312</v>
+        <v>61</v>
       </c>
       <c r="B92" t="s">
-        <v>313</v>
+        <v>353</v>
       </c>
       <c r="C92" t="s">
-        <v>314</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>336</v>
+        <v>274</v>
       </c>
       <c r="B93" t="s">
-        <v>337</v>
+        <v>445</v>
       </c>
       <c r="C93" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>345</v>
+        <v>125</v>
       </c>
       <c r="B94" t="s">
-        <v>346</v>
+        <v>384</v>
       </c>
       <c r="C94" t="s">
-        <v>347</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>318</v>
+        <v>255</v>
       </c>
       <c r="B95" t="s">
-        <v>319</v>
+        <v>440</v>
       </c>
       <c r="C95" t="s">
-        <v>320</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>300</v>
+        <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>301</v>
+        <v>373</v>
       </c>
       <c r="C96" t="s">
-        <v>302</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>442</v>
       </c>
       <c r="C97" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>279</v>
+        <v>231</v>
       </c>
       <c r="B98" t="s">
-        <v>280</v>
+        <v>431</v>
       </c>
       <c r="C98" t="s">
-        <v>281</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="B99" t="s">
-        <v>253</v>
+        <v>364</v>
       </c>
       <c r="C99" t="s">
-        <v>254</v>
+        <v>84</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>309</v>
+        <v>79</v>
       </c>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>362</v>
       </c>
       <c r="C100" t="s">
-        <v>311</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>276</v>
+        <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="C101" t="s">
-        <v>278</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>270</v>
+        <v>219</v>
       </c>
       <c r="B102" t="s">
-        <v>271</v>
+        <v>425</v>
       </c>
       <c r="C102" t="s">
-        <v>272</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>342</v>
+        <v>87</v>
       </c>
       <c r="B103" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C103" t="s">
-        <v>344</v>
+        <v>88</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>240</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>241</v>
+        <v>383</v>
       </c>
       <c r="C104" t="s">
-        <v>242</v>
+        <v>122</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="B105" t="s">
-        <v>307</v>
+        <v>436</v>
       </c>
       <c r="C105" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="B106" t="s">
-        <v>325</v>
+        <v>439</v>
       </c>
       <c r="C106" t="s">
-        <v>326</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>264</v>
+        <v>139</v>
       </c>
       <c r="B107" t="s">
-        <v>265</v>
+        <v>341</v>
       </c>
       <c r="C107" t="s">
-        <v>266</v>
+        <v>140</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>255</v>
+        <v>192</v>
       </c>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>410</v>
       </c>
       <c r="C108" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B109" t="s">
-        <v>286</v>
+        <v>461</v>
       </c>
       <c r="C109" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="B110" t="s">
-        <v>316</v>
+        <v>451</v>
       </c>
       <c r="C110" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>288</v>
+        <v>223</v>
       </c>
       <c r="B111" t="s">
-        <v>289</v>
+        <v>427</v>
       </c>
       <c r="C111" t="s">
-        <v>290</v>
+        <v>224</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>249</v>
+        <v>281</v>
       </c>
       <c r="B112" t="s">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C112" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>273</v>
+        <v>150</v>
       </c>
       <c r="B113" t="s">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="C113" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>348</v>
+        <v>40</v>
       </c>
       <c r="B114" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C114" t="s">
-        <v>350</v>
+        <v>41</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>303</v>
+        <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C115" t="s">
-        <v>305</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>354</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
         <v>355</v>
       </c>
       <c r="C116" t="s">
-        <v>356</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>294</v>
+        <v>81</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>363</v>
       </c>
       <c r="C117" t="s">
-        <v>296</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>465</v>
       </c>
       <c r="C118" t="s">
-        <v>341</v>
+        <v>300</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>258</v>
+        <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>259</v>
+        <v>380</v>
       </c>
       <c r="C119" t="s">
-        <v>260</v>
+        <v>116</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>333</v>
+        <v>99</v>
       </c>
       <c r="B120" t="s">
-        <v>334</v>
+        <v>372</v>
       </c>
       <c r="C120" t="s">
-        <v>335</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="B121" t="s">
-        <v>328</v>
+        <v>376</v>
       </c>
       <c r="C121" t="s">
-        <v>329</v>
+        <v>108</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>405</v>
+        <v>227</v>
       </c>
       <c r="B122" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="C122" t="s">
-        <v>407</v>
+        <v>228</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>393</v>
+        <v>233</v>
       </c>
       <c r="B123" t="s">
-        <v>394</v>
+        <v>432</v>
       </c>
       <c r="C123" t="s">
-        <v>395</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>408</v>
+        <v>36</v>
       </c>
       <c r="B124" t="s">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="C124" t="s">
-        <v>410</v>
+        <v>37</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>372</v>
+        <v>154</v>
       </c>
       <c r="B125" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C125" t="s">
-        <v>374</v>
+        <v>155</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>396</v>
+        <v>225</v>
       </c>
       <c r="B126" t="s">
-        <v>397</v>
+        <v>428</v>
       </c>
       <c r="C126" t="s">
-        <v>398</v>
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>402</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>403</v>
+        <v>343</v>
       </c>
       <c r="C127" t="s">
-        <v>404</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>390</v>
+        <v>198</v>
       </c>
       <c r="B128" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C128" t="s">
-        <v>392</v>
+        <v>199</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>369</v>
+        <v>147</v>
       </c>
       <c r="B129" t="s">
-        <v>370</v>
+        <v>345</v>
       </c>
       <c r="C129" t="s">
-        <v>371</v>
+        <v>148</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>363</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="C130" t="s">
-        <v>365</v>
+        <v>302</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>411</v>
+        <v>63</v>
       </c>
       <c r="B131" t="s">
-        <v>412</v>
+        <v>354</v>
       </c>
       <c r="C131" t="s">
-        <v>413</v>
+        <v>64</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>375</v>
+        <v>75</v>
       </c>
       <c r="B132" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C132" t="s">
-        <v>377</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>360</v>
+        <v>221</v>
       </c>
       <c r="B133" t="s">
-        <v>361</v>
+        <v>426</v>
       </c>
       <c r="C133" t="s">
-        <v>362</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>378</v>
+        <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="C134" t="s">
-        <v>380</v>
+        <v>134</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>387</v>
+        <v>238</v>
       </c>
       <c r="B135" t="s">
-        <v>388</v>
+        <v>433</v>
       </c>
       <c r="C135" t="s">
-        <v>389</v>
+        <v>239</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>414</v>
+        <v>111</v>
       </c>
       <c r="B136" t="s">
-        <v>415</v>
+        <v>378</v>
       </c>
       <c r="C136" t="s">
-        <v>416</v>
+        <v>112</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>384</v>
+        <v>202</v>
       </c>
       <c r="B137" t="s">
-        <v>385</v>
+        <v>415</v>
       </c>
       <c r="C137" t="s">
-        <v>386</v>
+        <v>203</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>399</v>
+        <v>143</v>
       </c>
       <c r="B138" t="s">
-        <v>400</v>
+        <v>344</v>
       </c>
       <c r="C138" t="s">
-        <v>401</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>381</v>
+        <v>260</v>
       </c>
       <c r="B139" t="s">
-        <v>382</v>
+        <v>441</v>
       </c>
       <c r="C139" t="s">
-        <v>383</v>
+        <v>261</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>366</v>
+        <v>276</v>
       </c>
       <c r="B140" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="C140" t="s">
-        <v>368</v>
+        <v>277</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="B141" t="s">
-        <v>418</v>
+        <v>443</v>
       </c>
       <c r="C141" t="s">
-        <v>419</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>474</v>
+        <v>105</v>
       </c>
       <c r="B142" t="s">
-        <v>475</v>
+        <v>375</v>
       </c>
       <c r="C142" t="s">
-        <v>476</v>
+        <v>106</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>483</v>
+        <v>321</v>
       </c>
       <c r="B143" t="s">
-        <v>484</v>
+        <v>322</v>
       </c>
       <c r="C143" t="s">
-        <v>485</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="B144" t="s">
-        <v>439</v>
+        <v>336</v>
       </c>
       <c r="C144" t="s">
-        <v>440</v>
+        <v>55</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="B145" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="C145" t="s">
-        <v>473</v>
+        <v>278</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>498</v>
+        <v>434</v>
       </c>
       <c r="B146" t="s">
-        <v>499</v>
+        <v>435</v>
       </c>
       <c r="C146" t="s">
-        <v>500</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>423</v>
+        <v>347</v>
       </c>
       <c r="B147" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
       <c r="C147" t="s">
-        <v>425</v>
+        <v>149</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B148" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="C148" t="s">
-        <v>455</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="B149" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="C149" t="s">
-        <v>446</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>441</v>
+        <v>337</v>
       </c>
       <c r="B150" t="s">
-        <v>442</v>
+        <v>338</v>
       </c>
       <c r="C150" t="s">
-        <v>443</v>
+        <v>56</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>480</v>
+        <v>389</v>
       </c>
       <c r="B151" t="s">
-        <v>481</v>
+        <v>390</v>
       </c>
       <c r="C151" t="s">
-        <v>482</v>
+        <v>305</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B152" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C152" t="s">
-        <v>461</v>
+        <v>288</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="B153" t="s">
-        <v>448</v>
+        <v>420</v>
       </c>
       <c r="C153" t="s">
-        <v>449</v>
+        <v>210</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>501</v>
+        <v>457</v>
       </c>
       <c r="B154" t="s">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="C154" t="s">
-        <v>503</v>
+        <v>289</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>429</v>
+        <v>312</v>
       </c>
       <c r="B155" t="s">
-        <v>430</v>
+        <v>313</v>
       </c>
       <c r="C155" t="s">
-        <v>431</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="B156" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="C156" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>435</v>
-      </c>
-      <c r="B157" t="s">
-        <v>436</v>
-      </c>
-      <c r="C157" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>492</v>
-      </c>
-      <c r="B158" t="s">
-        <v>493</v>
-      </c>
-      <c r="C158" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>456</v>
-      </c>
-      <c r="B159" t="s">
-        <v>457</v>
-      </c>
-      <c r="C159" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>516</v>
-      </c>
-      <c r="B160" t="s">
-        <v>517</v>
-      </c>
-      <c r="C160" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>450</v>
-      </c>
-      <c r="B161" t="s">
-        <v>451</v>
-      </c>
-      <c r="C161" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A162" t="s">
-        <v>513</v>
-      </c>
-      <c r="B162" t="s">
-        <v>514</v>
-      </c>
-      <c r="C162" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A163" t="s">
-        <v>432</v>
-      </c>
-      <c r="B163" t="s">
-        <v>433</v>
-      </c>
-      <c r="C163" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A164" t="s">
-        <v>420</v>
-      </c>
-      <c r="B164" t="s">
-        <v>421</v>
-      </c>
-      <c r="C164" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A165" t="s">
-        <v>486</v>
-      </c>
-      <c r="B165" t="s">
-        <v>487</v>
-      </c>
-      <c r="C165" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A166" t="s">
-        <v>468</v>
-      </c>
-      <c r="B166" t="s">
-        <v>469</v>
-      </c>
-      <c r="C166" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>495</v>
-      </c>
-      <c r="B167" t="s">
-        <v>496</v>
-      </c>
-      <c r="C167" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>504</v>
-      </c>
-      <c r="B168" t="s">
-        <v>505</v>
-      </c>
-      <c r="C168" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A169" t="s">
-        <v>510</v>
-      </c>
-      <c r="B169" t="s">
-        <v>511</v>
-      </c>
-      <c r="C169" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A170" t="s">
-        <v>462</v>
-      </c>
-      <c r="B170" t="s">
-        <v>463</v>
-      </c>
-      <c r="C170" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A171" t="s">
-        <v>489</v>
-      </c>
-      <c r="B171" t="s">
-        <v>490</v>
-      </c>
-      <c r="C171" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A172" t="s">
-        <v>507</v>
-      </c>
-      <c r="B172" t="s">
-        <v>508</v>
-      </c>
-      <c r="C172" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A173" t="s">
-        <v>477</v>
-      </c>
-      <c r="B173" t="s">
-        <v>478</v>
-      </c>
-      <c r="C173" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A174" t="s">
-        <v>465</v>
-      </c>
-      <c r="B174" t="s">
-        <v>466</v>
-      </c>
-      <c r="C174" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A175" t="s">
-        <v>555</v>
-      </c>
-      <c r="B175" t="s">
-        <v>556</v>
-      </c>
-      <c r="C175" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A176" t="s">
-        <v>543</v>
-      </c>
-      <c r="B176" t="s">
-        <v>544</v>
-      </c>
-      <c r="C176" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A177" t="s">
-        <v>540</v>
-      </c>
-      <c r="B177" t="s">
-        <v>541</v>
-      </c>
-      <c r="C177" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A178" t="s">
-        <v>546</v>
-      </c>
-      <c r="B178" t="s">
-        <v>547</v>
-      </c>
-      <c r="C178" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A179" t="s">
-        <v>531</v>
-      </c>
-      <c r="B179" t="s">
-        <v>532</v>
-      </c>
-      <c r="C179" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A180" t="s">
-        <v>552</v>
-      </c>
-      <c r="B180" t="s">
-        <v>553</v>
-      </c>
-      <c r="C180" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A181" t="s">
-        <v>525</v>
-      </c>
-      <c r="B181" t="s">
-        <v>526</v>
-      </c>
-      <c r="C181" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A182" t="s">
-        <v>528</v>
-      </c>
-      <c r="B182" t="s">
-        <v>529</v>
-      </c>
-      <c r="C182" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" t="s">
-        <v>549</v>
-      </c>
-      <c r="B183" t="s">
-        <v>550</v>
-      </c>
-      <c r="C183" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A184" t="s">
-        <v>558</v>
-      </c>
-      <c r="B184" t="s">
-        <v>559</v>
-      </c>
-      <c r="C184" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>534</v>
-      </c>
-      <c r="B185" t="s">
-        <v>535</v>
-      </c>
-      <c r="C185" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" t="s">
-        <v>519</v>
-      </c>
-      <c r="B186" t="s">
-        <v>520</v>
-      </c>
-      <c r="C186" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A187" t="s">
-        <v>537</v>
-      </c>
-      <c r="B187" t="s">
-        <v>538</v>
-      </c>
-      <c r="C187" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A188" t="s">
-        <v>561</v>
-      </c>
-      <c r="B188" t="s">
-        <v>562</v>
-      </c>
-      <c r="C188" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A189" t="s">
-        <v>522</v>
-      </c>
-      <c r="B189" t="s">
-        <v>523</v>
-      </c>
-      <c r="C189" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A190" t="s">
-        <v>606</v>
-      </c>
-      <c r="B190" t="s">
-        <v>607</v>
-      </c>
-      <c r="C190" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A191" t="s">
-        <v>690</v>
-      </c>
-      <c r="B191" t="s">
-        <v>691</v>
-      </c>
-      <c r="C191" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A192" t="s">
-        <v>651</v>
-      </c>
-      <c r="B192" t="s">
-        <v>652</v>
-      </c>
-      <c r="C192" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A193" t="s">
-        <v>603</v>
-      </c>
-      <c r="B193" t="s">
-        <v>604</v>
-      </c>
-      <c r="C193" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A194" t="s">
-        <v>564</v>
-      </c>
-      <c r="B194" t="s">
-        <v>565</v>
-      </c>
-      <c r="C194" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A195" t="s">
-        <v>621</v>
-      </c>
-      <c r="B195" t="s">
-        <v>622</v>
-      </c>
-      <c r="C195" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A196" t="s">
-        <v>597</v>
-      </c>
-      <c r="B196" t="s">
-        <v>598</v>
-      </c>
-      <c r="C196" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A197" t="s">
-        <v>699</v>
-      </c>
-      <c r="B197" t="s">
-        <v>700</v>
-      </c>
-      <c r="C197" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A198" t="s">
-        <v>660</v>
-      </c>
-      <c r="B198" t="s">
-        <v>661</v>
-      </c>
-      <c r="C198" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A199" t="s">
-        <v>645</v>
-      </c>
-      <c r="B199" t="s">
-        <v>646</v>
-      </c>
-      <c r="C199" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A200" t="s">
-        <v>609</v>
-      </c>
-      <c r="B200" t="s">
-        <v>610</v>
-      </c>
-      <c r="C200" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A201" t="s">
-        <v>669</v>
-      </c>
-      <c r="B201" t="s">
-        <v>670</v>
-      </c>
-      <c r="C201" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>585</v>
-      </c>
-      <c r="B202" t="s">
-        <v>586</v>
-      </c>
-      <c r="C202" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A203" t="s">
-        <v>573</v>
-      </c>
-      <c r="B203" t="s">
-        <v>574</v>
-      </c>
-      <c r="C203" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A204" t="s">
-        <v>615</v>
-      </c>
-      <c r="B204" t="s">
-        <v>616</v>
-      </c>
-      <c r="C204" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A205" t="s">
-        <v>630</v>
-      </c>
-      <c r="B205" t="s">
-        <v>631</v>
-      </c>
-      <c r="C205" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A206" t="s">
-        <v>612</v>
-      </c>
-      <c r="B206" t="s">
-        <v>613</v>
-      </c>
-      <c r="C206" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>627</v>
-      </c>
-      <c r="B207" t="s">
-        <v>628</v>
-      </c>
-      <c r="C207" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A208" t="s">
-        <v>654</v>
-      </c>
-      <c r="B208" t="s">
-        <v>655</v>
-      </c>
-      <c r="C208" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A209" t="s">
-        <v>684</v>
-      </c>
-      <c r="B209" t="s">
-        <v>685</v>
-      </c>
-      <c r="C209" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A210" t="s">
-        <v>582</v>
-      </c>
-      <c r="B210" t="s">
-        <v>583</v>
-      </c>
-      <c r="C210" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A211" t="s">
-        <v>678</v>
-      </c>
-      <c r="B211" t="s">
-        <v>679</v>
-      </c>
-      <c r="C211" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A212" t="s">
-        <v>657</v>
-      </c>
-      <c r="B212" t="s">
-        <v>658</v>
-      </c>
-      <c r="C212" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A213" t="s">
-        <v>624</v>
-      </c>
-      <c r="B213" t="s">
-        <v>625</v>
-      </c>
-      <c r="C213" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
-        <v>588</v>
-      </c>
-      <c r="B214" t="s">
-        <v>589</v>
-      </c>
-      <c r="C214" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A215" t="s">
-        <v>663</v>
-      </c>
-      <c r="B215" t="s">
-        <v>664</v>
-      </c>
-      <c r="C215" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A216" t="s">
-        <v>636</v>
-      </c>
-      <c r="B216" t="s">
-        <v>637</v>
-      </c>
-      <c r="C216" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>672</v>
-      </c>
-      <c r="B217" t="s">
-        <v>673</v>
-      </c>
-      <c r="C217" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A218" t="s">
-        <v>642</v>
-      </c>
-      <c r="B218" t="s">
-        <v>643</v>
-      </c>
-      <c r="C218" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A219" t="s">
-        <v>567</v>
-      </c>
-      <c r="B219" t="s">
-        <v>568</v>
-      </c>
-      <c r="C219" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A220" t="s">
-        <v>618</v>
-      </c>
-      <c r="B220" t="s">
-        <v>619</v>
-      </c>
-      <c r="C220" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A221" t="s">
-        <v>570</v>
-      </c>
-      <c r="B221" t="s">
-        <v>571</v>
-      </c>
-      <c r="C221" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A222" t="s">
-        <v>633</v>
-      </c>
-      <c r="B222" t="s">
-        <v>634</v>
-      </c>
-      <c r="C222" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A223" t="s">
-        <v>705</v>
-      </c>
-      <c r="B223" t="s">
-        <v>706</v>
-      </c>
-      <c r="C223" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" t="s">
-        <v>600</v>
-      </c>
-      <c r="B224" t="s">
-        <v>601</v>
-      </c>
-      <c r="C224" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" t="s">
-        <v>696</v>
-      </c>
-      <c r="B225" t="s">
-        <v>697</v>
-      </c>
-      <c r="C225" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A226" t="s">
-        <v>591</v>
-      </c>
-      <c r="B226" t="s">
-        <v>592</v>
-      </c>
-      <c r="C226" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A227" t="s">
-        <v>693</v>
-      </c>
-      <c r="B227" t="s">
-        <v>694</v>
-      </c>
-      <c r="C227" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A228" t="s">
-        <v>648</v>
-      </c>
-      <c r="B228" t="s">
-        <v>649</v>
-      </c>
-      <c r="C228" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A229" t="s">
-        <v>681</v>
-      </c>
-      <c r="B229" t="s">
-        <v>682</v>
-      </c>
-      <c r="C229" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A230" t="s">
-        <v>702</v>
-      </c>
-      <c r="B230" t="s">
-        <v>703</v>
-      </c>
-      <c r="C230" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A231" t="s">
-        <v>594</v>
-      </c>
-      <c r="B231" t="s">
-        <v>595</v>
-      </c>
-      <c r="C231" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" t="s">
-        <v>639</v>
-      </c>
-      <c r="B232" t="s">
-        <v>640</v>
-      </c>
-      <c r="C232" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" t="s">
-        <v>579</v>
-      </c>
-      <c r="B233" t="s">
-        <v>580</v>
-      </c>
-      <c r="C233" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A234" t="s">
-        <v>576</v>
-      </c>
-      <c r="B234" t="s">
-        <v>577</v>
-      </c>
-      <c r="C234" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A235" t="s">
-        <v>687</v>
-      </c>
-      <c r="B235" t="s">
-        <v>688</v>
-      </c>
-      <c r="C235" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A236" t="s">
-        <v>675</v>
-      </c>
-      <c r="B236" t="s">
-        <v>676</v>
-      </c>
-      <c r="C236" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A237" t="s">
-        <v>666</v>
-      </c>
-      <c r="B237" t="s">
-        <v>667</v>
-      </c>
-      <c r="C237" t="s">
-        <v>668</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C156">
+    <sortCondition ref="A2:A156"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>